--- a/docs/files/2026-10-12/상담행정공고_2026-10-12.xlsx
+++ b/docs/files/2026-10-12/상담행정공고_2026-10-12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -531,32 +531,24 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>청소년</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>의정부시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>정규직</t>
-        </is>
-      </c>
+          <t>[채용공고] 의정부시남자단기청소년쉼터 직원(팀원) 채용공고</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -567,17 +559,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -589,25 +581,29 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071991</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>구립동대문장애인종합복지관</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>구립동대문장애인종합복지관 직원 채용 공고 (성인지역사회누리팀 사회복지사-정규직, 아동청소년행복팀 작업치료사-육아휴직대체)</t>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -617,28 +613,28 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 동대문구</t>
+          <t>서울특별시 노원구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -650,56 +646,56 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1060700</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>사회복지법인 생명의전화</t>
+          <t>구립동대문장애인종합복지관</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
+          <t>구립동대문장애인종합복지관 직원 채용 공고 (성인지역사회누리팀 사회복지사-정규직, 아동청소년행복팀 작업치료사-육아휴직대체)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>계약직 · 대체인력</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>서울특별시 동대문구</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -711,56 +707,56 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>구립동대문장애인종합복지관</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>구립동대문장애인종합복지관 직원 채용 공고 (성인지역사회누리팀 사회복지사-정규직, 아동청소년행복팀 작업치료사-육아휴직대체)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>정규직 · 대체인력</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시 동대문구</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -772,7 +768,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1060700</t>
         </is>
       </c>
     </row>
@@ -785,12 +781,12 @@
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>우천복지재단</t>
+          <t>사회복지법인 생명의전화</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
+          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -800,7 +796,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -811,17 +807,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -833,25 +829,25 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -861,7 +857,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>서울특별시 양천구</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -872,17 +868,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -894,98 +890,86 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>교육</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>학교법인한국폴리텍</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>한국폴리텍대학 지역대학장 및 교육원장 공개초빙 공고</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>부산,경기,전남광주,경남,제주</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,석사,박사</t>
-        </is>
-      </c>
+          <t>서울특별시 금천구</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>* 임기: 2년(단, 임기 중 정년에 도달한 경우에는 정년 적용) * 정년: 65세(내부 지원자는 내규에 따른 정년 적용) * 기본 요건(포괄요건) - 기술, 기능인력 양성, 대학의 장기 발전전략 수립 및 추진, 대외협력사업, 교직원 능력개발 및 조직 역량 강화 등의 대학 경영을 원활하게 수행할 수 있는 업무추진력, 조직관리 능력 및 대외 협상능력을 갖춘 자 * 구체요건(학력요건) - 박사학위 가진 사람: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 - 석사학위 가진 사람: 공무원 또는 민간근무, 연구경력 8년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 * 구체요건(자격증요건) - 기술사, 기능장 소지자: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력이 3년 이상인 자 * 구체요건(경력요건) 1. 공무원 경력 - 관련분야에서 2년 이상 근무한 자로서 4급 또는 이에 상당하는 직급 이상의 공무원</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>해당사항 없음 해당사항 없음</t>
-        </is>
-      </c>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.kopo.ac.kr/board.do?menu=10523&amp;mode=view&amp;post=786443</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터 직원 채용공고</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 파주시</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1006,17 +990,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1028,41 +1012,45 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 교육</t>
+          <t>교육</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>율목종합사회복지관</t>
+          <t>학교법인한국폴리텍</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
+          <t>한국폴리텍대학 지역대학장 및 교육원장 공개초빙 공고</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>부산,경기,전남광주,경남,제주</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,석사,박사</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1072,52 +1060,60 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-8</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>* 임기: 2년(단, 임기 중 정년에 도달한 경우에는 정년 적용) * 정년: 65세(내부 지원자는 내규에 따른 정년 적용) * 기본 요건(포괄요건) - 기술, 기능인력 양성, 대학의 장기 발전전략 수립 및 추진, 대외협력사업, 교직원 능력개발 및 조직 역량 강화 등의 대학 경영을 원활하게 수행할 수 있는 업무추진력, 조직관리 능력 및 대외 협상능력을 갖춘 자 * 구체요건(학력요건) - 박사학위 가진 사람: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 - 석사학위 가진 사람: 공무원 또는 민간근무, 연구경력 8년 이상인 자로서 관련분야 근무, 연구경력 3년 이상인 자 * 구체요건(자격증요건) - 기술사, 기능장 소지자: 공무원 또는 민간근무, 연구경력 5년 이상인 자로서 관련분야 근무, 연구경력이 3년 이상인 자 * 구체요건(경력요건) 1. 공무원 경력 - 관련분야에서 2년 이상 근무한 자로서 4급 또는 이에 상당하는 직급 이상의 공무원</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>해당사항 없음 해당사항 없음</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
+          <t>https://www.kopo.ac.kr/board.do?menu=10523&amp;mode=view&amp;post=786443</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>솔이랑</t>
+          <t>경기북부청소년성문화센터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
+          <t>경기북부청소년성문화센터 직원 채용공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 중구</t>
+          <t>경기도 파주시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1128,17 +1124,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1150,12 +1146,378 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>시흥시남자단기청소년쉼터</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>안양시남자단기청소년쉼터</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>경기도 안양시</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>율목종합사회복지관</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>경기도 안양시 만안구</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>시흥장애인종합복지관</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>D-14</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>솔이랑</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>아담중증장애인거주시설</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 유성구</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>D-14</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
